--- a/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/3组磷硫铁法预实验-2.xlsx
+++ b/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/3组磷硫铁法预实验-2.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peiyuliu/Desktop/PKU-Undergraduate-Course-Public/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8EB32C-BBB5-A744-87D1-2E1E613AA228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="120" windowWidth="9435" windowHeight="6915"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="板 1 - Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,8 +19,42 @@
     <definedName name="MethodPointer1">-344778032</definedName>
     <definedName name="MethodPointer2">579</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -325,7 +365,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6">
     <font>
       <sz val="10"/>
@@ -554,15 +594,952 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-CN"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'板 1 - Sheet1'!$T$35:$T$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.13999999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.0000000000000016E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.0000000000000008E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.0000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0000000000000002E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'板 1 - Sheet1'!$V$35:$V$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>2.3094999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.9724999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.8055000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3265</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1254999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.82350000000000012</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.40099999999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.22649999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-389F-3647-8742-72C7229E5795}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1097757808"/>
+        <c:axId val="1297226768"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1097757808"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1297226768"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1297226768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1097757808"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>349250</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63D8637C-3E5A-4A45-84F4-34C572463B05}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -604,7 +1581,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -636,9 +1613,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -670,6 +1665,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -845,15 +1858,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:O32"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:AI94"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:18" ht="14">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -861,7 +1874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:18" ht="14">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -869,12 +1882,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:18" ht="14">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:18" ht="14">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -882,7 +1895,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:18" ht="14">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -890,7 +1903,7 @@
         <v>45618</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:18" ht="14">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -898,7 +1911,7 @@
         <v>0.7036458333333333</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:18" ht="14">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,7 +1919,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:18" ht="14">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -914,7 +1927,7 @@
         <v>19012425</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:18" ht="14">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -922,13 +1935,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:18" ht="14">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="5"/>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:18" ht="14">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -936,49 +1949,195 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:18" ht="14">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:18" ht="14">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="Q16" s="14"/>
+      <c r="R16" s="14"/>
+    </row>
+    <row r="17" spans="1:22" ht="14">
       <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="Q17" s="14">
+        <v>3.5720000000000001</v>
+      </c>
+      <c r="R17" s="14">
+        <v>3.5150000000000001</v>
+      </c>
+      <c r="S17">
+        <v>10</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <f t="shared" ref="U17:U47" si="0">(Q17+R17)/2</f>
+        <v>3.5434999999999999</v>
+      </c>
+      <c r="V17">
+        <f t="shared" ref="V17:V46" si="1">U17-0.063</f>
+        <v>3.4804999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="14">
       <c r="B18" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="Q18" s="13">
+        <v>3.355</v>
+      </c>
+      <c r="R18" s="14">
+        <v>3.5089999999999999</v>
+      </c>
+      <c r="S18">
+        <v>9</v>
+      </c>
+      <c r="T18">
+        <v>0.9</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="0"/>
+        <v>3.4319999999999999</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="1"/>
+        <v>3.3689999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="14">
       <c r="B19" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="Q19" s="14">
+        <v>3.68</v>
+      </c>
+      <c r="R19" s="13">
+        <v>3.3860000000000001</v>
+      </c>
+      <c r="S19">
+        <v>8</v>
+      </c>
+      <c r="T19">
+        <v>0.8</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="0"/>
+        <v>3.5330000000000004</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="1"/>
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
+      <c r="Q20" s="14">
+        <v>3.5510000000000002</v>
+      </c>
+      <c r="R20" s="14">
+        <v>3.694</v>
+      </c>
+      <c r="S20">
+        <v>7</v>
+      </c>
+      <c r="T20">
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="0"/>
+        <v>3.6225000000000001</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="1"/>
+        <v>3.5594999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="14">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="5"/>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="Q21" s="14">
+        <v>3.5059999999999998</v>
+      </c>
+      <c r="R21" s="14">
+        <v>3.4580000000000002</v>
+      </c>
+      <c r="S21">
+        <v>6</v>
+      </c>
+      <c r="T21">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="0"/>
+        <v>3.4820000000000002</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="1"/>
+        <v>3.419</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="14">
       <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B22">
         <v>24.1</v>
       </c>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="Q22" s="14">
+        <v>3.496</v>
+      </c>
+      <c r="R22" s="14">
+        <v>3.6080000000000001</v>
+      </c>
+      <c r="S22">
+        <v>5</v>
+      </c>
+      <c r="T22">
+        <v>0.5</v>
+      </c>
+      <c r="U22">
+        <f t="shared" si="0"/>
+        <v>3.552</v>
+      </c>
+      <c r="V22">
+        <f t="shared" si="1"/>
+        <v>3.4889999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
+      <c r="Q23" s="13">
+        <v>3.4260000000000002</v>
+      </c>
+      <c r="R23" s="14">
+        <v>3.444</v>
+      </c>
+      <c r="S23">
+        <v>4</v>
+      </c>
+      <c r="T23">
+        <v>0.4</v>
+      </c>
+      <c r="U23">
+        <f t="shared" si="0"/>
+        <v>3.4350000000000001</v>
+      </c>
+      <c r="V23">
+        <f t="shared" si="1"/>
+        <v>3.3719999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="B24" s="6"/>
       <c r="C24" s="7">
         <v>1</v>
@@ -1016,8 +2175,28 @@
       <c r="N24" s="7">
         <v>12</v>
       </c>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="Q24" s="12">
+        <v>3.169</v>
+      </c>
+      <c r="R24" s="13">
+        <v>3.2210000000000001</v>
+      </c>
+      <c r="S24">
+        <v>3.6</v>
+      </c>
+      <c r="T24">
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="U24">
+        <f t="shared" si="0"/>
+        <v>3.1950000000000003</v>
+      </c>
+      <c r="V24">
+        <f t="shared" si="1"/>
+        <v>3.1320000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="14">
       <c r="B25" s="7" t="s">
         <v>25</v>
       </c>
@@ -1060,8 +2239,28 @@
       <c r="O25" s="16">
         <v>560</v>
       </c>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="Q25" s="12">
+        <v>3.121</v>
+      </c>
+      <c r="R25" s="12">
+        <v>3.1589999999999998</v>
+      </c>
+      <c r="S25">
+        <v>3.4</v>
+      </c>
+      <c r="T25">
+        <v>0.34</v>
+      </c>
+      <c r="U25">
+        <f t="shared" si="0"/>
+        <v>3.1399999999999997</v>
+      </c>
+      <c r="V25">
+        <f t="shared" si="1"/>
+        <v>3.0769999999999995</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="14">
       <c r="B26" s="7" t="s">
         <v>26</v>
       </c>
@@ -1104,8 +2303,28 @@
       <c r="O26" s="16">
         <v>560</v>
       </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="Q26" s="13">
+        <v>3.2730000000000001</v>
+      </c>
+      <c r="R26" s="13">
+        <v>3.2650000000000001</v>
+      </c>
+      <c r="S26">
+        <v>3.2</v>
+      </c>
+      <c r="T26">
+        <v>0.32000000000000006</v>
+      </c>
+      <c r="U26">
+        <f t="shared" si="0"/>
+        <v>3.2690000000000001</v>
+      </c>
+      <c r="V26">
+        <f t="shared" si="1"/>
+        <v>3.206</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="14">
       <c r="B27" s="7" t="s">
         <v>27</v>
       </c>
@@ -1148,8 +2367,28 @@
       <c r="O27" s="16">
         <v>560</v>
       </c>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="Q27" s="11">
+        <v>2.738</v>
+      </c>
+      <c r="R27" s="12">
+        <v>3.121</v>
+      </c>
+      <c r="S27">
+        <v>3</v>
+      </c>
+      <c r="T27">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="U27">
+        <f t="shared" si="0"/>
+        <v>2.9295</v>
+      </c>
+      <c r="V27">
+        <f t="shared" si="1"/>
+        <v>2.8664999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="14">
       <c r="B28" s="7" t="s">
         <v>28</v>
       </c>
@@ -1192,8 +2431,28 @@
       <c r="O28" s="16">
         <v>560</v>
       </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="Q28" s="12">
+        <v>2.9430000000000001</v>
+      </c>
+      <c r="R28" s="12">
+        <v>3.1389999999999998</v>
+      </c>
+      <c r="S28">
+        <v>2.8</v>
+      </c>
+      <c r="T28">
+        <v>0.27999999999999997</v>
+      </c>
+      <c r="U28">
+        <f t="shared" si="0"/>
+        <v>3.0409999999999999</v>
+      </c>
+      <c r="V28">
+        <f t="shared" si="1"/>
+        <v>2.9779999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="14">
       <c r="B29" s="7" t="s">
         <v>29</v>
       </c>
@@ -1236,8 +2495,28 @@
       <c r="O29" s="16">
         <v>560</v>
       </c>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="Q29" s="12">
+        <v>3.1019999999999999</v>
+      </c>
+      <c r="R29" s="13">
+        <v>3.194</v>
+      </c>
+      <c r="S29">
+        <v>2.6</v>
+      </c>
+      <c r="T29">
+        <v>0.26</v>
+      </c>
+      <c r="U29">
+        <f t="shared" si="0"/>
+        <v>3.1479999999999997</v>
+      </c>
+      <c r="V29">
+        <f t="shared" si="1"/>
+        <v>3.0849999999999995</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="14">
       <c r="B30" s="7" t="s">
         <v>30</v>
       </c>
@@ -1280,8 +2559,28 @@
       <c r="O30" s="16">
         <v>560</v>
       </c>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="Q30" s="11">
+        <v>2.7389999999999999</v>
+      </c>
+      <c r="R30" s="11">
+        <v>2.863</v>
+      </c>
+      <c r="S30">
+        <v>2.4</v>
+      </c>
+      <c r="T30">
+        <v>0.24</v>
+      </c>
+      <c r="U30">
+        <f t="shared" si="0"/>
+        <v>2.8010000000000002</v>
+      </c>
+      <c r="V30">
+        <f t="shared" si="1"/>
+        <v>2.738</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="14">
       <c r="B31" s="7" t="s">
         <v>31</v>
       </c>
@@ -1324,8 +2623,28 @@
       <c r="O31" s="16">
         <v>560</v>
       </c>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="Q31" s="11">
+        <v>2.653</v>
+      </c>
+      <c r="R31" s="12">
+        <v>2.9119999999999999</v>
+      </c>
+      <c r="S31">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="T31">
+        <v>0.22000000000000003</v>
+      </c>
+      <c r="U31">
+        <f t="shared" si="0"/>
+        <v>2.7824999999999998</v>
+      </c>
+      <c r="V31">
+        <f t="shared" si="1"/>
+        <v>2.7194999999999996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="14">
       <c r="B32" s="7" t="s">
         <v>32</v>
       </c>
@@ -1368,11 +2687,1442 @@
       <c r="O32" s="16">
         <v>560</v>
       </c>
+      <c r="Q32" s="10">
+        <v>2.41</v>
+      </c>
+      <c r="R32" s="11">
+        <v>2.6880000000000002</v>
+      </c>
+      <c r="S32">
+        <v>2</v>
+      </c>
+      <c r="T32">
+        <v>0.2</v>
+      </c>
+      <c r="U32">
+        <f t="shared" si="0"/>
+        <v>2.5490000000000004</v>
+      </c>
+      <c r="V32">
+        <f t="shared" si="1"/>
+        <v>2.4860000000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="17:22">
+      <c r="Q33" s="10">
+        <v>2.423</v>
+      </c>
+      <c r="R33" s="11">
+        <v>2.722</v>
+      </c>
+      <c r="S33">
+        <v>1.8</v>
+      </c>
+      <c r="T33">
+        <v>0.18000000000000002</v>
+      </c>
+      <c r="U33">
+        <f t="shared" si="0"/>
+        <v>2.5724999999999998</v>
+      </c>
+      <c r="V33">
+        <f t="shared" si="1"/>
+        <v>2.5094999999999996</v>
+      </c>
+    </row>
+    <row r="34" spans="17:22">
+      <c r="Q34" s="18">
+        <v>2.282</v>
+      </c>
+      <c r="R34" s="18">
+        <v>2.3450000000000002</v>
+      </c>
+      <c r="S34">
+        <v>1.6</v>
+      </c>
+      <c r="T34">
+        <v>0.16000000000000003</v>
+      </c>
+      <c r="U34">
+        <f t="shared" si="0"/>
+        <v>2.3135000000000003</v>
+      </c>
+      <c r="V34">
+        <f t="shared" si="1"/>
+        <v>2.2505000000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="17:22">
+      <c r="Q35" s="10">
+        <v>2.5110000000000001</v>
+      </c>
+      <c r="R35" s="18">
+        <v>2.234</v>
+      </c>
+      <c r="S35">
+        <v>1.4</v>
+      </c>
+      <c r="T35">
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="U35">
+        <f t="shared" si="0"/>
+        <v>2.3725000000000001</v>
+      </c>
+      <c r="V35">
+        <f t="shared" si="1"/>
+        <v>2.3094999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="17:22">
+      <c r="Q36" s="22">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="R36" s="22">
+        <v>2.0459999999999998</v>
+      </c>
+      <c r="S36">
+        <v>1.2</v>
+      </c>
+      <c r="T36">
+        <v>0.12</v>
+      </c>
+      <c r="U36">
+        <f t="shared" si="0"/>
+        <v>2.0354999999999999</v>
+      </c>
+      <c r="V36">
+        <f t="shared" si="1"/>
+        <v>1.9724999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="17:22">
+      <c r="Q37" s="22">
+        <v>2.0619999999999998</v>
+      </c>
+      <c r="R37" s="21">
+        <v>1.675</v>
+      </c>
+      <c r="S37">
+        <v>1</v>
+      </c>
+      <c r="T37">
+        <v>0.1</v>
+      </c>
+      <c r="U37">
+        <f t="shared" si="0"/>
+        <v>1.8685</v>
+      </c>
+      <c r="V37">
+        <f t="shared" si="1"/>
+        <v>1.8055000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="17:22">
+      <c r="Q38" s="20">
+        <v>1.1990000000000001</v>
+      </c>
+      <c r="R38" s="19">
+        <v>1.58</v>
+      </c>
+      <c r="S38">
+        <v>0.8</v>
+      </c>
+      <c r="T38">
+        <v>8.0000000000000016E-2</v>
+      </c>
+      <c r="U38">
+        <f t="shared" si="0"/>
+        <v>1.3895</v>
+      </c>
+      <c r="V38">
+        <f t="shared" si="1"/>
+        <v>1.3265</v>
+      </c>
+    </row>
+    <row r="39" spans="17:22">
+      <c r="Q39" s="20">
+        <v>1.141</v>
+      </c>
+      <c r="R39" s="20">
+        <v>1.236</v>
+      </c>
+      <c r="S39">
+        <v>0.6</v>
+      </c>
+      <c r="T39">
+        <v>0.06</v>
+      </c>
+      <c r="U39">
+        <f t="shared" si="0"/>
+        <v>1.1884999999999999</v>
+      </c>
+      <c r="V39">
+        <f t="shared" si="1"/>
+        <v>1.1254999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="17:22">
+      <c r="Q40" s="8">
+        <v>0.79</v>
+      </c>
+      <c r="R40" s="9">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="S40">
+        <v>0.4</v>
+      </c>
+      <c r="T40">
+        <v>4.0000000000000008E-2</v>
+      </c>
+      <c r="U40">
+        <f t="shared" si="0"/>
+        <v>0.88650000000000007</v>
+      </c>
+      <c r="V40">
+        <f t="shared" si="1"/>
+        <v>0.82350000000000012</v>
+      </c>
+    </row>
+    <row r="41" spans="17:22">
+      <c r="Q41" s="17">
+        <v>0.44900000000000001</v>
+      </c>
+      <c r="R41" s="17">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="S41">
+        <v>0.2</v>
+      </c>
+      <c r="T41">
+        <v>2.0000000000000004E-2</v>
+      </c>
+      <c r="U41">
+        <f t="shared" si="0"/>
+        <v>0.46399999999999997</v>
+      </c>
+      <c r="V41">
+        <f t="shared" si="1"/>
+        <v>0.40099999999999997</v>
+      </c>
+    </row>
+    <row r="42" spans="17:22">
+      <c r="Q42" s="15">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="R42" s="15">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="S42">
+        <v>0.1</v>
+      </c>
+      <c r="T42">
+        <v>1.0000000000000002E-2</v>
+      </c>
+      <c r="U42">
+        <f t="shared" si="0"/>
+        <v>0.28949999999999998</v>
+      </c>
+      <c r="V42">
+        <f t="shared" si="1"/>
+        <v>0.22649999999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="17:22">
+      <c r="Q43" s="19">
+        <v>1.4339999999999999</v>
+      </c>
+      <c r="R43" s="20">
+        <v>1.3220000000000001</v>
+      </c>
+      <c r="S43">
+        <v>0.08</v>
+      </c>
+      <c r="T43">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="U43">
+        <f t="shared" si="0"/>
+        <v>1.3780000000000001</v>
+      </c>
+      <c r="V43">
+        <f t="shared" si="1"/>
+        <v>1.3150000000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="17:22">
+      <c r="Q44" s="8">
+        <v>0.73</v>
+      </c>
+      <c r="R44" s="8">
+        <v>0.75700000000000001</v>
+      </c>
+      <c r="S44">
+        <v>0.04</v>
+      </c>
+      <c r="T44">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="U44">
+        <f t="shared" si="0"/>
+        <v>0.74350000000000005</v>
+      </c>
+      <c r="V44">
+        <f t="shared" si="1"/>
+        <v>0.6805000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="17:22">
+      <c r="Q45" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="R45" s="17">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="S45">
+        <v>0.02</v>
+      </c>
+      <c r="T45">
+        <v>2E-3</v>
+      </c>
+      <c r="U45">
+        <f t="shared" si="0"/>
+        <v>0.46850000000000003</v>
+      </c>
+      <c r="V45">
+        <f t="shared" si="1"/>
+        <v>0.40550000000000003</v>
+      </c>
+    </row>
+    <row r="46" spans="17:22">
+      <c r="Q46" s="15">
+        <v>0.215</v>
+      </c>
+      <c r="R46" s="15">
+        <v>0.217</v>
+      </c>
+      <c r="S46">
+        <v>0.01</v>
+      </c>
+      <c r="T46">
+        <v>1E-3</v>
+      </c>
+      <c r="U46">
+        <f t="shared" si="0"/>
+        <v>0.216</v>
+      </c>
+      <c r="V46">
+        <f t="shared" si="1"/>
+        <v>0.153</v>
+      </c>
+    </row>
+    <row r="47" spans="17:22">
+      <c r="Q47" s="15">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="R47" s="15">
+        <v>6.2E-2</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <f t="shared" si="0"/>
+        <v>6.3E-2</v>
+      </c>
+      <c r="V47">
+        <f>U47-0.063</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="4:25">
+      <c r="R56">
+        <v>1</v>
+      </c>
+      <c r="S56">
+        <v>2</v>
+      </c>
+      <c r="T56">
+        <v>3</v>
+      </c>
+      <c r="U56">
+        <v>4</v>
+      </c>
+      <c r="V56">
+        <v>5</v>
+      </c>
+      <c r="W56">
+        <v>6</v>
+      </c>
+      <c r="X56">
+        <v>7</v>
+      </c>
+      <c r="Y56">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="4:25">
+      <c r="D57">
+        <v>0.79</v>
+      </c>
+      <c r="E57">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="F57">
+        <v>2.41</v>
+      </c>
+      <c r="G57">
+        <v>2.6880000000000002</v>
+      </c>
+      <c r="H57">
+        <v>3.169</v>
+      </c>
+      <c r="I57">
+        <v>3.2210000000000001</v>
+      </c>
+      <c r="J57">
+        <v>3.5720000000000001</v>
+      </c>
+      <c r="K57">
+        <v>3.5150000000000001</v>
+      </c>
+      <c r="L57">
+        <v>0.154</v>
+      </c>
+      <c r="M57">
+        <v>0.157</v>
+      </c>
+      <c r="N57">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="O57">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="R57" cm="1">
+        <f t="array" ref="R57:Y68">TRANSPOSE(D57:O64)</f>
+        <v>0.79</v>
+      </c>
+      <c r="S57">
+        <v>0.44900000000000001</v>
+      </c>
+      <c r="T57">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="U57">
+        <v>1.4339999999999999</v>
+      </c>
+      <c r="V57">
+        <v>0.73</v>
+      </c>
+      <c r="W57">
+        <v>0.45</v>
+      </c>
+      <c r="X57">
+        <v>0.215</v>
+      </c>
+      <c r="Y57">
+        <v>6.4000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="4:25">
+      <c r="D58">
+        <v>0.44900000000000001</v>
+      </c>
+      <c r="E58">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="F58">
+        <v>2.423</v>
+      </c>
+      <c r="G58">
+        <v>2.722</v>
+      </c>
+      <c r="H58">
+        <v>3.121</v>
+      </c>
+      <c r="I58">
+        <v>3.1589999999999998</v>
+      </c>
+      <c r="J58">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="K58">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="L58">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="M58">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="N58">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="O58">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="R58">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="S58">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="T58">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="U58">
+        <v>1.3220000000000001</v>
+      </c>
+      <c r="V58">
+        <v>0.75700000000000001</v>
+      </c>
+      <c r="W58">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="X58">
+        <v>0.217</v>
+      </c>
+      <c r="Y58">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="4:25">
+      <c r="D59">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="E59">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F59">
+        <v>2.282</v>
+      </c>
+      <c r="G59">
+        <v>2.3450000000000002</v>
+      </c>
+      <c r="H59">
+        <v>3.2730000000000001</v>
+      </c>
+      <c r="I59">
+        <v>3.2650000000000001</v>
+      </c>
+      <c r="J59">
+        <v>3.355</v>
+      </c>
+      <c r="K59">
+        <v>3.5089999999999999</v>
+      </c>
+      <c r="L59">
+        <v>0.496</v>
+      </c>
+      <c r="M59">
+        <v>0.505</v>
+      </c>
+      <c r="N59">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="O59">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="R59">
+        <v>2.41</v>
+      </c>
+      <c r="S59">
+        <v>2.423</v>
+      </c>
+      <c r="T59">
+        <v>2.282</v>
+      </c>
+      <c r="U59">
+        <v>2.5110000000000001</v>
+      </c>
+      <c r="V59">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="W59">
+        <v>2.0619999999999998</v>
+      </c>
+      <c r="X59">
+        <v>1.1990000000000001</v>
+      </c>
+      <c r="Y59">
+        <v>1.141</v>
+      </c>
+    </row>
+    <row r="60" spans="4:25">
+      <c r="D60">
+        <v>1.4339999999999999</v>
+      </c>
+      <c r="E60">
+        <v>1.3220000000000001</v>
+      </c>
+      <c r="F60">
+        <v>2.5110000000000001</v>
+      </c>
+      <c r="G60">
+        <v>2.234</v>
+      </c>
+      <c r="H60">
+        <v>2.738</v>
+      </c>
+      <c r="I60">
+        <v>3.121</v>
+      </c>
+      <c r="J60">
+        <v>3.68</v>
+      </c>
+      <c r="K60">
+        <v>3.3860000000000001</v>
+      </c>
+      <c r="L60">
+        <v>1.861</v>
+      </c>
+      <c r="M60">
+        <v>1.887</v>
+      </c>
+      <c r="N60">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="O60">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="R60">
+        <v>2.6880000000000002</v>
+      </c>
+      <c r="S60">
+        <v>2.722</v>
+      </c>
+      <c r="T60">
+        <v>2.3450000000000002</v>
+      </c>
+      <c r="U60">
+        <v>2.234</v>
+      </c>
+      <c r="V60">
+        <v>2.0459999999999998</v>
+      </c>
+      <c r="W60">
+        <v>1.675</v>
+      </c>
+      <c r="X60">
+        <v>1.58</v>
+      </c>
+      <c r="Y60">
+        <v>1.236</v>
+      </c>
+    </row>
+    <row r="61" spans="4:25">
+      <c r="D61">
+        <v>0.73</v>
+      </c>
+      <c r="E61">
+        <v>0.75700000000000001</v>
+      </c>
+      <c r="F61">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="G61">
+        <v>2.0459999999999998</v>
+      </c>
+      <c r="H61">
+        <v>2.9430000000000001</v>
+      </c>
+      <c r="I61">
+        <v>3.1389999999999998</v>
+      </c>
+      <c r="J61">
+        <v>3.5510000000000002</v>
+      </c>
+      <c r="K61">
+        <v>3.694</v>
+      </c>
+      <c r="L61">
+        <v>0.08</v>
+      </c>
+      <c r="M61">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="N61">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="O61">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="R61">
+        <v>3.169</v>
+      </c>
+      <c r="S61">
+        <v>3.121</v>
+      </c>
+      <c r="T61">
+        <v>3.2730000000000001</v>
+      </c>
+      <c r="U61">
+        <v>2.738</v>
+      </c>
+      <c r="V61">
+        <v>2.9430000000000001</v>
+      </c>
+      <c r="W61">
+        <v>3.1019999999999999</v>
+      </c>
+      <c r="X61">
+        <v>2.7389999999999999</v>
+      </c>
+      <c r="Y61">
+        <v>2.653</v>
+      </c>
+    </row>
+    <row r="62" spans="4:25">
+      <c r="D62">
+        <v>0.45</v>
+      </c>
+      <c r="E62">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="F62">
+        <v>2.0619999999999998</v>
+      </c>
+      <c r="G62">
+        <v>1.675</v>
+      </c>
+      <c r="H62">
+        <v>3.1019999999999999</v>
+      </c>
+      <c r="I62">
+        <v>3.194</v>
+      </c>
+      <c r="J62">
+        <v>3.5059999999999998</v>
+      </c>
+      <c r="K62">
+        <v>3.4580000000000002</v>
+      </c>
+      <c r="L62">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="M62">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="N62">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="O62">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="R62">
+        <v>3.2210000000000001</v>
+      </c>
+      <c r="S62">
+        <v>3.1589999999999998</v>
+      </c>
+      <c r="T62">
+        <v>3.2650000000000001</v>
+      </c>
+      <c r="U62">
+        <v>3.121</v>
+      </c>
+      <c r="V62">
+        <v>3.1389999999999998</v>
+      </c>
+      <c r="W62">
+        <v>3.194</v>
+      </c>
+      <c r="X62">
+        <v>2.863</v>
+      </c>
+      <c r="Y62">
+        <v>2.9119999999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="4:25">
+      <c r="D63">
+        <v>0.215</v>
+      </c>
+      <c r="E63">
+        <v>0.217</v>
+      </c>
+      <c r="F63">
+        <v>1.1990000000000001</v>
+      </c>
+      <c r="G63">
+        <v>1.58</v>
+      </c>
+      <c r="H63">
+        <v>2.7389999999999999</v>
+      </c>
+      <c r="I63">
+        <v>2.863</v>
+      </c>
+      <c r="J63">
+        <v>3.496</v>
+      </c>
+      <c r="K63">
+        <v>3.6080000000000001</v>
+      </c>
+      <c r="L63">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M63">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="N63">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="O63">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="R63">
+        <v>3.5720000000000001</v>
+      </c>
+      <c r="S63">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="T63">
+        <v>3.355</v>
+      </c>
+      <c r="U63">
+        <v>3.68</v>
+      </c>
+      <c r="V63">
+        <v>3.5510000000000002</v>
+      </c>
+      <c r="W63">
+        <v>3.5059999999999998</v>
+      </c>
+      <c r="X63">
+        <v>3.496</v>
+      </c>
+      <c r="Y63">
+        <v>3.4260000000000002</v>
+      </c>
+    </row>
+    <row r="64" spans="4:25">
+      <c r="D64">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="E64">
+        <v>6.2E-2</v>
+      </c>
+      <c r="F64">
+        <v>1.141</v>
+      </c>
+      <c r="G64">
+        <v>1.236</v>
+      </c>
+      <c r="H64">
+        <v>2.653</v>
+      </c>
+      <c r="I64">
+        <v>2.9119999999999999</v>
+      </c>
+      <c r="J64">
+        <v>3.4260000000000002</v>
+      </c>
+      <c r="K64">
+        <v>3.444</v>
+      </c>
+      <c r="L64">
+        <v>0.43</v>
+      </c>
+      <c r="M64">
+        <v>0.44</v>
+      </c>
+      <c r="N64">
+        <v>2.0979999999999999</v>
+      </c>
+      <c r="O64">
+        <v>2.0310000000000001</v>
+      </c>
+      <c r="R64">
+        <v>3.5150000000000001</v>
+      </c>
+      <c r="S64">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="T64">
+        <v>3.5089999999999999</v>
+      </c>
+      <c r="U64">
+        <v>3.3860000000000001</v>
+      </c>
+      <c r="V64">
+        <v>3.694</v>
+      </c>
+      <c r="W64">
+        <v>3.4580000000000002</v>
+      </c>
+      <c r="X64">
+        <v>3.6080000000000001</v>
+      </c>
+      <c r="Y64">
+        <v>3.444</v>
+      </c>
+    </row>
+    <row r="65" spans="18:25">
+      <c r="R65">
+        <v>0.154</v>
+      </c>
+      <c r="S65">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="T65">
+        <v>0.496</v>
+      </c>
+      <c r="U65">
+        <v>1.861</v>
+      </c>
+      <c r="V65">
+        <v>0.08</v>
+      </c>
+      <c r="W65">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="X65">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Y65">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="66" spans="18:25">
+      <c r="R66">
+        <v>0.157</v>
+      </c>
+      <c r="S66">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="T66">
+        <v>0.505</v>
+      </c>
+      <c r="U66">
+        <v>1.887</v>
+      </c>
+      <c r="V66">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="W66">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="X66">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="Y66">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="67" spans="18:25">
+      <c r="R67">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="S67">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="T67">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="U67">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="V67">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="W67">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="X67">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="Y67">
+        <v>2.0979999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="18:25">
+      <c r="R68">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="S68">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="T68">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="U68">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="V68">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="W68">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="X68">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="Y68">
+        <v>2.0310000000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="19:35">
+      <c r="S82">
+        <v>8</v>
+      </c>
+      <c r="T82">
+        <v>7</v>
+      </c>
+      <c r="U82">
+        <v>6</v>
+      </c>
+      <c r="V82">
+        <v>5</v>
+      </c>
+      <c r="W82">
+        <v>4</v>
+      </c>
+      <c r="X82">
+        <v>3</v>
+      </c>
+      <c r="Y82">
+        <v>2</v>
+      </c>
+      <c r="Z82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="19:35">
+      <c r="S83">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="T83">
+        <v>0.215</v>
+      </c>
+      <c r="U83">
+        <v>0.45</v>
+      </c>
+      <c r="V83">
+        <v>0.73</v>
+      </c>
+      <c r="W83">
+        <v>1.4339999999999999</v>
+      </c>
+      <c r="X83">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="Y83">
+        <v>0.44900000000000001</v>
+      </c>
+      <c r="Z83">
+        <v>0.79</v>
+      </c>
+      <c r="AB83">
+        <v>2.0979999999999999</v>
+      </c>
+      <c r="AC83">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="AD83">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="AE83">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="AF83">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="AG83">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="AH83">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="AI83">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="19:35">
+      <c r="S84">
+        <v>6.2E-2</v>
+      </c>
+      <c r="T84">
+        <v>0.217</v>
+      </c>
+      <c r="U84">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="V84">
+        <v>0.75700000000000001</v>
+      </c>
+      <c r="W84">
+        <v>1.3220000000000001</v>
+      </c>
+      <c r="X84">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="Y84">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="Z84">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="AB84">
+        <v>2.0310000000000001</v>
+      </c>
+      <c r="AC84">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="AD84">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="AE84">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="AF84">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="AG84">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="AH84">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="AI84">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="19:35">
+      <c r="S85">
+        <v>1.141</v>
+      </c>
+      <c r="T85">
+        <v>1.1990000000000001</v>
+      </c>
+      <c r="U85">
+        <v>2.0619999999999998</v>
+      </c>
+      <c r="V85">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="W85">
+        <v>2.5110000000000001</v>
+      </c>
+      <c r="X85">
+        <v>2.282</v>
+      </c>
+      <c r="Y85">
+        <v>2.423</v>
+      </c>
+      <c r="Z85">
+        <v>2.41</v>
+      </c>
+      <c r="AB85">
+        <f>(AB83+AB84)/2</f>
+        <v>2.0644999999999998</v>
+      </c>
+      <c r="AC85">
+        <f t="shared" ref="AC85:AI85" si="2">(AC83+AC84)/2</f>
+        <v>0.6</v>
+      </c>
+      <c r="AD85">
+        <f t="shared" si="2"/>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="AE85">
+        <f t="shared" si="2"/>
+        <v>0.18</v>
+      </c>
+      <c r="AF85">
+        <f t="shared" si="2"/>
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="AG85">
+        <f t="shared" si="2"/>
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="AH85">
+        <f t="shared" si="2"/>
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="AI85">
+        <f t="shared" si="2"/>
+        <v>4.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="19:35">
+      <c r="S86">
+        <v>1.236</v>
+      </c>
+      <c r="T86">
+        <v>1.58</v>
+      </c>
+      <c r="U86">
+        <v>1.675</v>
+      </c>
+      <c r="V86">
+        <v>2.0459999999999998</v>
+      </c>
+      <c r="W86">
+        <v>2.234</v>
+      </c>
+      <c r="X86">
+        <v>2.3450000000000002</v>
+      </c>
+      <c r="Y86">
+        <v>2.722</v>
+      </c>
+      <c r="Z86">
+        <v>2.6880000000000002</v>
+      </c>
+      <c r="AB86">
+        <f>ABS(AB83-AB84)</f>
+        <v>6.6999999999999726E-2</v>
+      </c>
+      <c r="AC86">
+        <f t="shared" ref="AC86:AI86" si="3">ABS(AC83-AC84)</f>
+        <v>3.6000000000000032E-2</v>
+      </c>
+      <c r="AD86">
+        <f t="shared" si="3"/>
+        <v>8.0000000000000071E-3</v>
+      </c>
+      <c r="AE86">
+        <f t="shared" si="3"/>
+        <v>2.7999999999999997E-2</v>
+      </c>
+      <c r="AF86">
+        <f t="shared" si="3"/>
+        <v>1.0000000000000009E-3</v>
+      </c>
+      <c r="AG86">
+        <f t="shared" si="3"/>
+        <v>2.0000000000000018E-3</v>
+      </c>
+      <c r="AH86">
+        <f t="shared" si="3"/>
+        <v>2.0000000000000018E-3</v>
+      </c>
+      <c r="AI86">
+        <f t="shared" si="3"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="87" spans="19:35">
+      <c r="S87">
+        <v>2.653</v>
+      </c>
+      <c r="T87">
+        <v>2.7389999999999999</v>
+      </c>
+      <c r="U87">
+        <v>3.1019999999999999</v>
+      </c>
+      <c r="V87">
+        <v>2.9430000000000001</v>
+      </c>
+      <c r="W87">
+        <v>2.738</v>
+      </c>
+      <c r="X87">
+        <v>3.2730000000000001</v>
+      </c>
+      <c r="Y87">
+        <v>3.121</v>
+      </c>
+      <c r="Z87">
+        <v>3.169</v>
+      </c>
+    </row>
+    <row r="88" spans="19:35">
+      <c r="S88">
+        <v>2.9119999999999999</v>
+      </c>
+      <c r="T88">
+        <v>2.863</v>
+      </c>
+      <c r="U88">
+        <v>3.194</v>
+      </c>
+      <c r="V88">
+        <v>3.1389999999999998</v>
+      </c>
+      <c r="W88">
+        <v>3.121</v>
+      </c>
+      <c r="X88">
+        <v>3.2650000000000001</v>
+      </c>
+      <c r="Y88">
+        <v>3.1589999999999998</v>
+      </c>
+      <c r="Z88">
+        <v>3.2210000000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="19:35">
+      <c r="S89">
+        <v>3.4260000000000002</v>
+      </c>
+      <c r="T89">
+        <v>3.496</v>
+      </c>
+      <c r="U89">
+        <v>3.5059999999999998</v>
+      </c>
+      <c r="V89">
+        <v>3.5510000000000002</v>
+      </c>
+      <c r="W89">
+        <v>3.68</v>
+      </c>
+      <c r="X89">
+        <v>3.355</v>
+      </c>
+      <c r="Y89">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="Z89">
+        <v>3.5720000000000001</v>
+      </c>
+    </row>
+    <row r="90" spans="19:35">
+      <c r="S90">
+        <v>3.444</v>
+      </c>
+      <c r="T90">
+        <v>3.6080000000000001</v>
+      </c>
+      <c r="U90">
+        <v>3.4580000000000002</v>
+      </c>
+      <c r="V90">
+        <v>3.694</v>
+      </c>
+      <c r="W90">
+        <v>3.3860000000000001</v>
+      </c>
+      <c r="X90">
+        <v>3.5089999999999999</v>
+      </c>
+      <c r="Y90">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="Z90">
+        <v>3.5150000000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="19:35">
+      <c r="S91">
+        <v>0.43</v>
+      </c>
+      <c r="T91">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="U91">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="V91">
+        <v>0.08</v>
+      </c>
+      <c r="W91">
+        <v>1.861</v>
+      </c>
+      <c r="X91">
+        <v>0.496</v>
+      </c>
+      <c r="Y91">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="Z91">
+        <v>0.154</v>
+      </c>
+    </row>
+    <row r="92" spans="19:35">
+      <c r="S92">
+        <v>0.44</v>
+      </c>
+      <c r="T92">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="U92">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="V92">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="W92">
+        <v>1.887</v>
+      </c>
+      <c r="X92">
+        <v>0.505</v>
+      </c>
+      <c r="Y92">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="Z92">
+        <v>0.157</v>
+      </c>
+    </row>
+    <row r="93" spans="19:35">
+      <c r="S93">
+        <v>2.0979999999999999</v>
+      </c>
+      <c r="T93">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="U93">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="V93">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="W93">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="X93">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="Y93">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="Z93">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="19:35">
+      <c r="S94">
+        <v>2.0310000000000001</v>
+      </c>
+      <c r="T94">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="U94">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="V94">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="W94">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="X94">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="Y94">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="Z94">
+        <v>4.3999999999999997E-2</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="S82:Z94">
+    <sortCondition descending="1" ref="S82:Z82"/>
+  </sortState>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="256" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>